--- a/backend/database/golive_20260501/golive_template.xlsx
+++ b/backend/database/golive_20260501/golive_template.xlsx
@@ -10,7 +10,6 @@
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Main_Stock" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="User_Stock" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Machine_Stock" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,10 +512,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -532,94 +531,94 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>วิธีใช้งานสั้น ๆ</t>
+          <t>Flow ใหม่ — เริ่มเติมตู้ก่อน · ระบบดึงสต็อกตู้จาก VMS อัตโนมัติ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1) เปิด tab 'Main_Stock'  →  กรอก full_boxes / loose_packs / unit_cost_per_pack ครบทุก SKU</t>
+          <t>1) แอดมินเติมของจริงในตู้ทุกตู้ให้เต็ม (เช้า ~07:00-08:30)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (ถ้า SKU ไหนไม่มีของเลย ใส่ 0 ทั้ง full_boxes และ loose_packs)</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2) ทีมเทคกด 'ดึงข้อมูล VMS' บนเว็บ → รอ ~1 นาที</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2) เปิด tab 'User_Stock'  →  กรอก 1 row ต่อ (ผู้ใช้, SKU) ที่ผู้ใช้ถือไว้ส่วนตัว</t>
+          <t>3) ตรวจหน้า 'สต็อกหน้าตู้' ว่าระบบเห็นตรงกับ VMS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (ถ้าผู้ใช้คนไหนไม่ถือของ ข้ามได้)</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>4) แอดมินนับสต็อกที่เหลือในมือ (User_Stock) + นับ Main → กรอกใน Excel นี้</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>3) เปิด tab 'Machine_Stock' → กรอกของในตู้ (optional · ข้ามได้ถ้า VMS sync ปกติ)</t>
+          <t>5) Save → ส่งไฟล์ให้ทีมเทค → reset + seed → go-live</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>4) Save ไฟล์ → ส่งให้ทีมเทคโนแลก่อนเช้า 1 พ.ค.</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>วิธีกรอก Sheet 'Main_Stock'</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>เงื่อนไขสำคัญ</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>• full_cottons = ลังใหญ่ครบ (1 cotton = 12 box · OP/EB = 144 packs · PRB = 120 packs)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• full_boxes = กล่องที่ครบเต็ม · loose_packs = ซองที่ไม่ครบกล่อง</t>
+          <t>• full_boxes = กล่องครบที่ไม่ได้อยู่ในลัง</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>• packs_per_box: OP/EB = 12 · PRB = 10 (ระบบมีให้ดู column C)</t>
+          <t>• loose_packs = ซองที่ไม่ครบกล่อง</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>• total_packs ระบบคำนวณให้อัตโนมัติ = full_boxes × packs_per_box + loose_packs</t>
+          <t>• total_packs = ระบบคำนวณให้อัตโนมัติ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>• unit_cost_per_pack: ใช้ราคาใบเสร็จล่าสุด (option B ที่ตกลงกัน)</t>
+          <t>• unit_cost_per_pack = ราคาทุน/ซอง (ใบเสร็จล่าสุด)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>• username ใน Sheet User_Stock ต้องตรงกับใน User Reference ทุกตัวอักษร</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>• ถ้าไม่มี SKU ไหนเลย ใส่ 0 ทุกช่อง</t>
         </is>
       </c>
     </row>
@@ -629,35 +628,35 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>ห้ามแก้</t>
+          <t>วิธีกรอก Sheet 'User_Stock'</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>• Sheet README นี้</t>
+          <t>• username ต้องตรงกับ User Reference ด้านล่างของ sheet</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>• Column A, B, C ใน Main_Stock (sku_id / series / packs_per_box)</t>
+          <t>• 1 row = 1 ผู้ใช้ × 1 SKU (เพิ่ม row ตามต้องการ)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>• User Reference ด้านล่าง User_Stock</t>
+          <t>• total_packs = ซองที่ผู้ใช้คนนั้น 'เหลือในมือ' หลังจากเติมตู้แล้ว</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>• Machine Reference ด้านล่าง Machine_Stock</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>• ถ้าผู้ใช้ไม่มี SKU ใดเลย ข้ามได้</t>
         </is>
       </c>
     </row>
@@ -667,14 +666,45 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>ติดต่อ</t>
+          <t>ห้ามแก้</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ถ้ามีคำถามหรือเจอช่องที่ไม่แน่ใจ → ทักเจ้าของระบบทันที (อย่าเดา)</t>
+          <t>• Sheet README นี้</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>• Column A-D ใน Main_Stock (sku_id / series / packs_per_box / packs_per_cotton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>• User Reference ด้านล่าง User_Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>คำถาม</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ถ้าไม่แน่ใจ → ทักเจ้าของระบบ (อย่าเดา) · ตัวเลขผิดยอดสต็อกพังหมดเดือน</t>
         </is>
       </c>
     </row>
@@ -689,17 +719,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -712,7 +744,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>กรอกเฉพาะ column สีครีม: full_boxes (กล่อง) · loose_packs (ซองที่ไม่ครบกล่อง) · unit_cost_per_pack (ราคาทุน/ซอง · ใบเสร็จล่าสุด) · note (ถ้ามี)</t>
+          <t>กรอกเฉพาะ column สีครีม: full_cottons (ลังใหญ่ครบ) · full_boxes (กล่องครบ) · loose_packs (ซองเหลือ) · unit_cost_per_pack (ราคาใบเสร็จล่าสุด) · note</t>
         </is>
       </c>
     </row>
@@ -734,25 +766,35 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
+          <t>packs_per_cotton</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>full_cottons</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>full_boxes</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>loose_packs</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>total_packs (auto)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>unit_cost_per_pack</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -772,20 +814,26 @@
       <c r="C4" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="7" t="n">
-        <v>0</v>
+      <c r="D4" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="8">
-        <f>D4*C4+E4</f>
+      <c r="F4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8">
+        <f>E4*D4+F4*C4+G4</f>
         <v/>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9" t="inlineStr"/>
+      <c r="I4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -801,20 +849,26 @@
       <c r="C5" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>0</v>
+      <c r="D5" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="8">
-        <f>D5*C5+E5</f>
+      <c r="F5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8">
+        <f>E5*D5+F5*C5+G5</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9" t="inlineStr"/>
+      <c r="I5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -830,20 +884,26 @@
       <c r="C6" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>0</v>
+      <c r="D6" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="8">
-        <f>D6*C6+E6</f>
+      <c r="F6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8">
+        <f>E6*D6+F6*C6+G6</f>
         <v/>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9" t="inlineStr"/>
+      <c r="I6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -859,20 +919,26 @@
       <c r="C7" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>0</v>
+      <c r="D7" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="8">
-        <f>D7*C7+E7</f>
+      <c r="F7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <f>E7*D7+F7*C7+G7</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="9" t="inlineStr"/>
+      <c r="I7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -888,20 +954,26 @@
       <c r="C8" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>0</v>
+      <c r="D8" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="8">
-        <f>D8*C8+E8</f>
+      <c r="F8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8">
+        <f>E8*D8+F8*C8+G8</f>
         <v/>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -917,20 +989,26 @@
       <c r="C9" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>0</v>
+      <c r="D9" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="8">
-        <f>D9*C9+E9</f>
+      <c r="F9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8">
+        <f>E9*D9+F9*C9+G9</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="9" t="inlineStr"/>
+      <c r="I9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -946,20 +1024,26 @@
       <c r="C10" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>0</v>
+      <c r="D10" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="8">
-        <f>D10*C10+E10</f>
+      <c r="F10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8">
+        <f>E10*D10+F10*C10+G10</f>
         <v/>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="9" t="inlineStr"/>
+      <c r="I10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -975,20 +1059,26 @@
       <c r="C11" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>0</v>
+      <c r="D11" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="8">
-        <f>D11*C11+E11</f>
+      <c r="F11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <f>E11*D11+F11*C11+G11</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1004,20 +1094,26 @@
       <c r="C12" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>0</v>
+      <c r="D12" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="8">
-        <f>D12*C12+E12</f>
+      <c r="F12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <f>E12*D12+F12*C12+G12</f>
         <v/>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1033,20 +1129,26 @@
       <c r="C13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>0</v>
+      <c r="D13" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="8">
-        <f>D13*C13+E13</f>
+      <c r="F13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <f>E13*D13+F13*C13+G13</f>
         <v/>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9" t="inlineStr"/>
+      <c r="I13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1062,20 +1164,26 @@
       <c r="C14" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D14" s="7" t="n">
-        <v>0</v>
+      <c r="D14" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="8">
-        <f>D14*C14+E14</f>
+      <c r="F14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8">
+        <f>E14*D14+F14*C14+G14</f>
         <v/>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1091,20 +1199,26 @@
       <c r="C15" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>0</v>
+      <c r="D15" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="8">
-        <f>D15*C15+E15</f>
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <f>E15*D15+F15*C15+G15</f>
         <v/>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1120,20 +1234,26 @@
       <c r="C16" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D16" s="7" t="n">
-        <v>0</v>
+      <c r="D16" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="8">
-        <f>D16*C16+E16</f>
+      <c r="F16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8">
+        <f>E16*D16+F16*C16+G16</f>
         <v/>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9" t="inlineStr"/>
+      <c r="I16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1149,20 +1269,26 @@
       <c r="C17" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D17" s="7" t="n">
-        <v>0</v>
+      <c r="D17" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="8">
-        <f>D17*C17+E17</f>
+      <c r="F17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <f>E17*D17+F17*C17+G17</f>
         <v/>
       </c>
-      <c r="G17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="9" t="inlineStr"/>
+      <c r="I17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1178,20 +1304,26 @@
       <c r="C18" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>0</v>
+      <c r="D18" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="8">
-        <f>D18*C18+E18</f>
+      <c r="F18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8">
+        <f>E18*D18+F18*C18+G18</f>
         <v/>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1207,20 +1339,26 @@
       <c r="C19" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D19" s="7" t="n">
-        <v>0</v>
+      <c r="D19" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="8">
-        <f>D19*C19+E19</f>
+      <c r="F19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <f>E19*D19+F19*C19+G19</f>
         <v/>
       </c>
-      <c r="G19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="9" t="inlineStr"/>
+      <c r="I19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1236,20 +1374,26 @@
       <c r="C20" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D20" s="7" t="n">
-        <v>0</v>
+      <c r="D20" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="8">
-        <f>D20*C20+E20</f>
+      <c r="F20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8">
+        <f>E20*D20+F20*C20+G20</f>
         <v/>
       </c>
-      <c r="G20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="9" t="inlineStr"/>
+      <c r="I20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1265,20 +1409,26 @@
       <c r="C21" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D21" s="7" t="n">
-        <v>0</v>
+      <c r="D21" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="8">
-        <f>D21*C21+E21</f>
+      <c r="F21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <f>E21*D21+F21*C21+G21</f>
         <v/>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="9" t="inlineStr"/>
+      <c r="I21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1294,20 +1444,26 @@
       <c r="C22" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D22" s="7" t="n">
-        <v>0</v>
+      <c r="D22" s="6" t="n">
+        <v>144</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="8">
-        <f>D22*C22+E22</f>
+      <c r="F22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8">
+        <f>E22*D22+F22*C22+G22</f>
         <v/>
       </c>
-      <c r="G22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="9" t="inlineStr"/>
+      <c r="I22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1323,20 +1479,26 @@
       <c r="C23" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="7" t="n">
-        <v>0</v>
+      <c r="D23" s="6" t="n">
+        <v>120</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="8">
-        <f>D23*C23+E23</f>
+      <c r="F23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <f>E23*D23+F23*C23+G23</f>
         <v/>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="9" t="inlineStr"/>
+      <c r="I23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1352,25 +1514,31 @@
       <c r="C24" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="7" t="n">
-        <v>0</v>
+      <c r="D24" s="6" t="n">
+        <v>120</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="8">
-        <f>D24*C24+E24</f>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="8">
+        <f>E24*D24+F24*C24+G24</f>
         <v/>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="9" t="inlineStr"/>
+      <c r="I24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1382,7 +1550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1395,14 +1563,14 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>👤 สต็อกที่แอดมินแต่ละคนถือไว้ส่วนตัว · ณ เช้า 1 พ.ค. 2026</t>
+          <t>👤 สต็อกที่แอดมินแต่ละคนถือเหลือ (หลังเติมตู้แล้ว) · ณ เช้า 1 พ.ค. 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>เพิ่ม 1 row ต่อ (ผู้ใช้, SKU) · ใส่ username ตามตาราง User Reference ด้านล่าง · total_packs = ซอง · ไม่ต้องใส่ราคา (ราคาดึงจาก Main)</t>
+          <t>เพิ่ม 1 row ต่อ (ผู้ใช้, SKU) · username ตรงกับ User Reference ด้านล่าง · total_packs = ซอง (ของที่เหลือในมือ ไม่รวมที่เติมไปในตู้แล้ว)</t>
         </is>
       </c>
     </row>
@@ -1783,110 +1951,180 @@
       <c r="D54" s="12" t="n"/>
       <c r="E54" s="12" t="n"/>
     </row>
+    <row r="55">
+      <c r="A55" s="12" t="n"/>
+      <c r="B55" s="12" t="n"/>
+      <c r="C55" s="12" t="n"/>
+      <c r="D55" s="12" t="n"/>
+      <c r="E55" s="12" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="n"/>
+      <c r="B56" s="12" t="n"/>
+      <c r="C56" s="12" t="n"/>
+      <c r="D56" s="12" t="n"/>
+      <c r="E56" s="12" t="n"/>
+    </row>
     <row r="57">
-      <c r="A57" s="13" t="inlineStr">
+      <c r="A57" s="12" t="n"/>
+      <c r="B57" s="12" t="n"/>
+      <c r="C57" s="12" t="n"/>
+      <c r="D57" s="12" t="n"/>
+      <c r="E57" s="12" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="n"/>
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="12" t="n"/>
+      <c r="D58" s="12" t="n"/>
+      <c r="E58" s="12" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="n"/>
+      <c r="B59" s="12" t="n"/>
+      <c r="C59" s="12" t="n"/>
+      <c r="D59" s="12" t="n"/>
+      <c r="E59" s="12" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="n"/>
+      <c r="B60" s="12" t="n"/>
+      <c r="C60" s="12" t="n"/>
+      <c r="D60" s="12" t="n"/>
+      <c r="E60" s="12" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="n"/>
+      <c r="B61" s="12" t="n"/>
+      <c r="C61" s="12" t="n"/>
+      <c r="D61" s="12" t="n"/>
+      <c r="E61" s="12" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="n"/>
+      <c r="B62" s="12" t="n"/>
+      <c r="C62" s="12" t="n"/>
+      <c r="D62" s="12" t="n"/>
+      <c r="E62" s="12" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="n"/>
+      <c r="B63" s="12" t="n"/>
+      <c r="C63" s="12" t="n"/>
+      <c r="D63" s="12" t="n"/>
+      <c r="E63" s="12" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="n"/>
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="12" t="n"/>
+      <c r="D64" s="12" t="n"/>
+      <c r="E64" s="12" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>👥 User Reference (อ้างอิง · อย่าแก้)</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="14" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr">
         <is>
           <t>username</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B68" s="14" t="inlineStr">
         <is>
           <t>display_name</t>
         </is>
       </c>
-      <c r="C58" s="14" t="inlineStr">
+      <c r="C68" s="14" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="15" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="15" t="inlineStr">
         <is>
           <t>divisionxcard</t>
         </is>
       </c>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="B69" s="15" t="inlineStr">
         <is>
           <t>DivisionX Card</t>
         </is>
       </c>
-      <c r="C59" s="15" t="inlineStr">
+      <c r="C69" s="15" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="15" t="inlineStr">
         <is>
           <t>pornthep_sm1991</t>
         </is>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B70" s="15" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="C60" s="15" t="inlineStr">
+      <c r="C70" s="15" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="15" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="15" t="inlineStr">
         <is>
           <t>aofwara66</t>
         </is>
       </c>
-      <c r="B61" s="15" t="inlineStr">
+      <c r="B71" s="15" t="inlineStr">
         <is>
           <t>AOFSEN</t>
         </is>
       </c>
-      <c r="C61" s="15" t="inlineStr">
+      <c r="C71" s="15" t="inlineStr">
         <is>
           <t>user</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="15" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="15" t="inlineStr">
         <is>
           <t>power23n</t>
         </is>
       </c>
-      <c r="B62" s="15" t="inlineStr">
+      <c r="B72" s="15" t="inlineStr">
         <is>
           <t>พี่ M</t>
         </is>
       </c>
-      <c r="C62" s="15" t="inlineStr">
+      <c r="C72" s="15" t="inlineStr">
         <is>
           <t>user</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="15" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
         <is>
           <t>mzadiz1989</t>
         </is>
       </c>
-      <c r="B63" s="15" t="inlineStr">
+      <c r="B73" s="15" t="inlineStr">
         <is>
           <t>M-zadiz</t>
         </is>
       </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="C73" s="15" t="inlineStr">
         <is>
           <t>user</t>
         </is>
@@ -1899,1049 +2137,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G112"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>🎰 สต็อกในตู้แต่ละช่อง · ณ เช้า 1 พ.ค. 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>optional sheet · ถ้าตู้ติด VMS sync ปกติแล้ว ไม่ต้องกรอกก็ได้ · ถ้ากรอก ระบบจะใช้บันทึกการเบิก Main → ตู้ตอนเริ่มใช้</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>machine_id</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>machine_name</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>slot_number</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>sku_id</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>remain</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>max_capacity</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="n"/>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="n"/>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="n"/>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="n"/>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="12" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="n"/>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="n"/>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="12" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="n"/>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="12" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="n"/>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="n"/>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="12" t="n"/>
-      <c r="G36" s="12" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="n"/>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="n"/>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="n"/>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="12" t="n"/>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="12" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="n"/>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="12" t="n"/>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="n"/>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="n"/>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="12" t="n"/>
-      <c r="F42" s="12" t="n"/>
-      <c r="G42" s="12" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="n"/>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="n"/>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="12" t="n"/>
-      <c r="G44" s="12" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="n"/>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="12" t="n"/>
-      <c r="G45" s="12" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="n"/>
-      <c r="B46" s="12" t="n"/>
-      <c r="C46" s="12" t="n"/>
-      <c r="D46" s="12" t="n"/>
-      <c r="E46" s="12" t="n"/>
-      <c r="F46" s="12" t="n"/>
-      <c r="G46" s="12" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="12" t="n"/>
-      <c r="B47" s="12" t="n"/>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="12" t="n"/>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="12" t="n"/>
-      <c r="G47" s="12" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="n"/>
-      <c r="B48" s="12" t="n"/>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="12" t="n"/>
-      <c r="E48" s="12" t="n"/>
-      <c r="F48" s="12" t="n"/>
-      <c r="G48" s="12" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="12" t="n"/>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="12" t="n"/>
-      <c r="E49" s="12" t="n"/>
-      <c r="F49" s="12" t="n"/>
-      <c r="G49" s="12" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="n"/>
-      <c r="B50" s="12" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="12" t="n"/>
-      <c r="G50" s="12" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="12" t="n"/>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="12" t="n"/>
-      <c r="E51" s="12" t="n"/>
-      <c r="F51" s="12" t="n"/>
-      <c r="G51" s="12" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="n"/>
-      <c r="B52" s="12" t="n"/>
-      <c r="C52" s="12" t="n"/>
-      <c r="D52" s="12" t="n"/>
-      <c r="E52" s="12" t="n"/>
-      <c r="F52" s="12" t="n"/>
-      <c r="G52" s="12" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="12" t="n"/>
-      <c r="B53" s="12" t="n"/>
-      <c r="C53" s="12" t="n"/>
-      <c r="D53" s="12" t="n"/>
-      <c r="E53" s="12" t="n"/>
-      <c r="F53" s="12" t="n"/>
-      <c r="G53" s="12" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="n"/>
-      <c r="B54" s="12" t="n"/>
-      <c r="C54" s="12" t="n"/>
-      <c r="D54" s="12" t="n"/>
-      <c r="E54" s="12" t="n"/>
-      <c r="F54" s="12" t="n"/>
-      <c r="G54" s="12" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="12" t="n"/>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="12" t="n"/>
-      <c r="E55" s="12" t="n"/>
-      <c r="F55" s="12" t="n"/>
-      <c r="G55" s="12" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="n"/>
-      <c r="B56" s="12" t="n"/>
-      <c r="C56" s="12" t="n"/>
-      <c r="D56" s="12" t="n"/>
-      <c r="E56" s="12" t="n"/>
-      <c r="F56" s="12" t="n"/>
-      <c r="G56" s="12" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="12" t="n"/>
-      <c r="B57" s="12" t="n"/>
-      <c r="C57" s="12" t="n"/>
-      <c r="D57" s="12" t="n"/>
-      <c r="E57" s="12" t="n"/>
-      <c r="F57" s="12" t="n"/>
-      <c r="G57" s="12" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="n"/>
-      <c r="B58" s="12" t="n"/>
-      <c r="C58" s="12" t="n"/>
-      <c r="D58" s="12" t="n"/>
-      <c r="E58" s="12" t="n"/>
-      <c r="F58" s="12" t="n"/>
-      <c r="G58" s="12" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="n"/>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="12" t="n"/>
-      <c r="F59" s="12" t="n"/>
-      <c r="G59" s="12" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="n"/>
-      <c r="B60" s="12" t="n"/>
-      <c r="C60" s="12" t="n"/>
-      <c r="D60" s="12" t="n"/>
-      <c r="E60" s="12" t="n"/>
-      <c r="F60" s="12" t="n"/>
-      <c r="G60" s="12" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="n"/>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="12" t="n"/>
-      <c r="D61" s="12" t="n"/>
-      <c r="E61" s="12" t="n"/>
-      <c r="F61" s="12" t="n"/>
-      <c r="G61" s="12" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="n"/>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="12" t="n"/>
-      <c r="D62" s="12" t="n"/>
-      <c r="E62" s="12" t="n"/>
-      <c r="F62" s="12" t="n"/>
-      <c r="G62" s="12" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="n"/>
-      <c r="B63" s="12" t="n"/>
-      <c r="C63" s="12" t="n"/>
-      <c r="D63" s="12" t="n"/>
-      <c r="E63" s="12" t="n"/>
-      <c r="F63" s="12" t="n"/>
-      <c r="G63" s="12" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="n"/>
-      <c r="B64" s="12" t="n"/>
-      <c r="C64" s="12" t="n"/>
-      <c r="D64" s="12" t="n"/>
-      <c r="E64" s="12" t="n"/>
-      <c r="F64" s="12" t="n"/>
-      <c r="G64" s="12" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="12" t="n"/>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="12" t="n"/>
-      <c r="D65" s="12" t="n"/>
-      <c r="E65" s="12" t="n"/>
-      <c r="F65" s="12" t="n"/>
-      <c r="G65" s="12" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="n"/>
-      <c r="B66" s="12" t="n"/>
-      <c r="C66" s="12" t="n"/>
-      <c r="D66" s="12" t="n"/>
-      <c r="E66" s="12" t="n"/>
-      <c r="F66" s="12" t="n"/>
-      <c r="G66" s="12" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="n"/>
-      <c r="B67" s="12" t="n"/>
-      <c r="C67" s="12" t="n"/>
-      <c r="D67" s="12" t="n"/>
-      <c r="E67" s="12" t="n"/>
-      <c r="F67" s="12" t="n"/>
-      <c r="G67" s="12" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="n"/>
-      <c r="B68" s="12" t="n"/>
-      <c r="C68" s="12" t="n"/>
-      <c r="D68" s="12" t="n"/>
-      <c r="E68" s="12" t="n"/>
-      <c r="F68" s="12" t="n"/>
-      <c r="G68" s="12" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="n"/>
-      <c r="B69" s="12" t="n"/>
-      <c r="C69" s="12" t="n"/>
-      <c r="D69" s="12" t="n"/>
-      <c r="E69" s="12" t="n"/>
-      <c r="F69" s="12" t="n"/>
-      <c r="G69" s="12" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="12" t="n"/>
-      <c r="B70" s="12" t="n"/>
-      <c r="C70" s="12" t="n"/>
-      <c r="D70" s="12" t="n"/>
-      <c r="E70" s="12" t="n"/>
-      <c r="F70" s="12" t="n"/>
-      <c r="G70" s="12" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="12" t="n"/>
-      <c r="B71" s="12" t="n"/>
-      <c r="C71" s="12" t="n"/>
-      <c r="D71" s="12" t="n"/>
-      <c r="E71" s="12" t="n"/>
-      <c r="F71" s="12" t="n"/>
-      <c r="G71" s="12" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="n"/>
-      <c r="B72" s="12" t="n"/>
-      <c r="C72" s="12" t="n"/>
-      <c r="D72" s="12" t="n"/>
-      <c r="E72" s="12" t="n"/>
-      <c r="F72" s="12" t="n"/>
-      <c r="G72" s="12" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="12" t="n"/>
-      <c r="B73" s="12" t="n"/>
-      <c r="C73" s="12" t="n"/>
-      <c r="D73" s="12" t="n"/>
-      <c r="E73" s="12" t="n"/>
-      <c r="F73" s="12" t="n"/>
-      <c r="G73" s="12" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="12" t="n"/>
-      <c r="B74" s="12" t="n"/>
-      <c r="C74" s="12" t="n"/>
-      <c r="D74" s="12" t="n"/>
-      <c r="E74" s="12" t="n"/>
-      <c r="F74" s="12" t="n"/>
-      <c r="G74" s="12" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="12" t="n"/>
-      <c r="B75" s="12" t="n"/>
-      <c r="C75" s="12" t="n"/>
-      <c r="D75" s="12" t="n"/>
-      <c r="E75" s="12" t="n"/>
-      <c r="F75" s="12" t="n"/>
-      <c r="G75" s="12" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="n"/>
-      <c r="B76" s="12" t="n"/>
-      <c r="C76" s="12" t="n"/>
-      <c r="D76" s="12" t="n"/>
-      <c r="E76" s="12" t="n"/>
-      <c r="F76" s="12" t="n"/>
-      <c r="G76" s="12" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="12" t="n"/>
-      <c r="B77" s="12" t="n"/>
-      <c r="C77" s="12" t="n"/>
-      <c r="D77" s="12" t="n"/>
-      <c r="E77" s="12" t="n"/>
-      <c r="F77" s="12" t="n"/>
-      <c r="G77" s="12" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="n"/>
-      <c r="B78" s="12" t="n"/>
-      <c r="C78" s="12" t="n"/>
-      <c r="D78" s="12" t="n"/>
-      <c r="E78" s="12" t="n"/>
-      <c r="F78" s="12" t="n"/>
-      <c r="G78" s="12" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="12" t="n"/>
-      <c r="B79" s="12" t="n"/>
-      <c r="C79" s="12" t="n"/>
-      <c r="D79" s="12" t="n"/>
-      <c r="E79" s="12" t="n"/>
-      <c r="F79" s="12" t="n"/>
-      <c r="G79" s="12" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="12" t="n"/>
-      <c r="B80" s="12" t="n"/>
-      <c r="C80" s="12" t="n"/>
-      <c r="D80" s="12" t="n"/>
-      <c r="E80" s="12" t="n"/>
-      <c r="F80" s="12" t="n"/>
-      <c r="G80" s="12" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="12" t="n"/>
-      <c r="B81" s="12" t="n"/>
-      <c r="C81" s="12" t="n"/>
-      <c r="D81" s="12" t="n"/>
-      <c r="E81" s="12" t="n"/>
-      <c r="F81" s="12" t="n"/>
-      <c r="G81" s="12" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="12" t="n"/>
-      <c r="B82" s="12" t="n"/>
-      <c r="C82" s="12" t="n"/>
-      <c r="D82" s="12" t="n"/>
-      <c r="E82" s="12" t="n"/>
-      <c r="F82" s="12" t="n"/>
-      <c r="G82" s="12" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="12" t="n"/>
-      <c r="B83" s="12" t="n"/>
-      <c r="C83" s="12" t="n"/>
-      <c r="D83" s="12" t="n"/>
-      <c r="E83" s="12" t="n"/>
-      <c r="F83" s="12" t="n"/>
-      <c r="G83" s="12" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="12" t="n"/>
-      <c r="B84" s="12" t="n"/>
-      <c r="C84" s="12" t="n"/>
-      <c r="D84" s="12" t="n"/>
-      <c r="E84" s="12" t="n"/>
-      <c r="F84" s="12" t="n"/>
-      <c r="G84" s="12" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="12" t="n"/>
-      <c r="B85" s="12" t="n"/>
-      <c r="C85" s="12" t="n"/>
-      <c r="D85" s="12" t="n"/>
-      <c r="E85" s="12" t="n"/>
-      <c r="F85" s="12" t="n"/>
-      <c r="G85" s="12" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="12" t="n"/>
-      <c r="B86" s="12" t="n"/>
-      <c r="C86" s="12" t="n"/>
-      <c r="D86" s="12" t="n"/>
-      <c r="E86" s="12" t="n"/>
-      <c r="F86" s="12" t="n"/>
-      <c r="G86" s="12" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="12" t="n"/>
-      <c r="B87" s="12" t="n"/>
-      <c r="C87" s="12" t="n"/>
-      <c r="D87" s="12" t="n"/>
-      <c r="E87" s="12" t="n"/>
-      <c r="F87" s="12" t="n"/>
-      <c r="G87" s="12" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="12" t="n"/>
-      <c r="B88" s="12" t="n"/>
-      <c r="C88" s="12" t="n"/>
-      <c r="D88" s="12" t="n"/>
-      <c r="E88" s="12" t="n"/>
-      <c r="F88" s="12" t="n"/>
-      <c r="G88" s="12" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="12" t="n"/>
-      <c r="B89" s="12" t="n"/>
-      <c r="C89" s="12" t="n"/>
-      <c r="D89" s="12" t="n"/>
-      <c r="E89" s="12" t="n"/>
-      <c r="F89" s="12" t="n"/>
-      <c r="G89" s="12" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="12" t="n"/>
-      <c r="B90" s="12" t="n"/>
-      <c r="C90" s="12" t="n"/>
-      <c r="D90" s="12" t="n"/>
-      <c r="E90" s="12" t="n"/>
-      <c r="F90" s="12" t="n"/>
-      <c r="G90" s="12" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="12" t="n"/>
-      <c r="B91" s="12" t="n"/>
-      <c r="C91" s="12" t="n"/>
-      <c r="D91" s="12" t="n"/>
-      <c r="E91" s="12" t="n"/>
-      <c r="F91" s="12" t="n"/>
-      <c r="G91" s="12" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="n"/>
-      <c r="B92" s="12" t="n"/>
-      <c r="C92" s="12" t="n"/>
-      <c r="D92" s="12" t="n"/>
-      <c r="E92" s="12" t="n"/>
-      <c r="F92" s="12" t="n"/>
-      <c r="G92" s="12" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="12" t="n"/>
-      <c r="B93" s="12" t="n"/>
-      <c r="C93" s="12" t="n"/>
-      <c r="D93" s="12" t="n"/>
-      <c r="E93" s="12" t="n"/>
-      <c r="F93" s="12" t="n"/>
-      <c r="G93" s="12" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="12" t="n"/>
-      <c r="B94" s="12" t="n"/>
-      <c r="C94" s="12" t="n"/>
-      <c r="D94" s="12" t="n"/>
-      <c r="E94" s="12" t="n"/>
-      <c r="F94" s="12" t="n"/>
-      <c r="G94" s="12" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="12" t="n"/>
-      <c r="B95" s="12" t="n"/>
-      <c r="C95" s="12" t="n"/>
-      <c r="D95" s="12" t="n"/>
-      <c r="E95" s="12" t="n"/>
-      <c r="F95" s="12" t="n"/>
-      <c r="G95" s="12" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="12" t="n"/>
-      <c r="B96" s="12" t="n"/>
-      <c r="C96" s="12" t="n"/>
-      <c r="D96" s="12" t="n"/>
-      <c r="E96" s="12" t="n"/>
-      <c r="F96" s="12" t="n"/>
-      <c r="G96" s="12" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="12" t="n"/>
-      <c r="B97" s="12" t="n"/>
-      <c r="C97" s="12" t="n"/>
-      <c r="D97" s="12" t="n"/>
-      <c r="E97" s="12" t="n"/>
-      <c r="F97" s="12" t="n"/>
-      <c r="G97" s="12" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="12" t="n"/>
-      <c r="B98" s="12" t="n"/>
-      <c r="C98" s="12" t="n"/>
-      <c r="D98" s="12" t="n"/>
-      <c r="E98" s="12" t="n"/>
-      <c r="F98" s="12" t="n"/>
-      <c r="G98" s="12" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="12" t="n"/>
-      <c r="B99" s="12" t="n"/>
-      <c r="C99" s="12" t="n"/>
-      <c r="D99" s="12" t="n"/>
-      <c r="E99" s="12" t="n"/>
-      <c r="F99" s="12" t="n"/>
-      <c r="G99" s="12" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="12" t="n"/>
-      <c r="B100" s="12" t="n"/>
-      <c r="C100" s="12" t="n"/>
-      <c r="D100" s="12" t="n"/>
-      <c r="E100" s="12" t="n"/>
-      <c r="F100" s="12" t="n"/>
-      <c r="G100" s="12" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="12" t="n"/>
-      <c r="B101" s="12" t="n"/>
-      <c r="C101" s="12" t="n"/>
-      <c r="D101" s="12" t="n"/>
-      <c r="E101" s="12" t="n"/>
-      <c r="F101" s="12" t="n"/>
-      <c r="G101" s="12" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="12" t="n"/>
-      <c r="B102" s="12" t="n"/>
-      <c r="C102" s="12" t="n"/>
-      <c r="D102" s="12" t="n"/>
-      <c r="E102" s="12" t="n"/>
-      <c r="F102" s="12" t="n"/>
-      <c r="G102" s="12" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="12" t="n"/>
-      <c r="B103" s="12" t="n"/>
-      <c r="C103" s="12" t="n"/>
-      <c r="D103" s="12" t="n"/>
-      <c r="E103" s="12" t="n"/>
-      <c r="F103" s="12" t="n"/>
-      <c r="G103" s="12" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="12" t="n"/>
-      <c r="B104" s="12" t="n"/>
-      <c r="C104" s="12" t="n"/>
-      <c r="D104" s="12" t="n"/>
-      <c r="E104" s="12" t="n"/>
-      <c r="F104" s="12" t="n"/>
-      <c r="G104" s="12" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="13" t="inlineStr">
-        <is>
-          <t>🎰 Machine Reference (อ้างอิง)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="14" t="inlineStr">
-        <is>
-          <t>machine_id</t>
-        </is>
-      </c>
-      <c r="B108" s="14" t="inlineStr">
-        <is>
-          <t>machine_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="15" t="inlineStr">
-        <is>
-          <t>chukes01</t>
-        </is>
-      </c>
-      <c r="B109" s="15" t="inlineStr">
-        <is>
-          <t>ตู้ 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="15" t="inlineStr">
-        <is>
-          <t>chukes02</t>
-        </is>
-      </c>
-      <c r="B110" s="15" t="inlineStr">
-        <is>
-          <t>ตู้ 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="15" t="inlineStr">
-        <is>
-          <t>chukes03</t>
-        </is>
-      </c>
-      <c r="B111" s="15" t="inlineStr">
-        <is>
-          <t>ตู้ 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="15" t="inlineStr">
-        <is>
-          <t>chukes04</t>
-        </is>
-      </c>
-      <c r="B112" s="15" t="inlineStr">
-        <is>
-          <t>ตู้ 4</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/backend/database/golive_20260501/golive_template.xlsx
+++ b/backend/database/golive_20260501/golive_template.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="115" customWidth="1" min="1" max="1"/>
@@ -581,23 +581,23 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>• full_cottons = ลังใหญ่ครบ (1 cotton = 12 box · OP/EB = 144 packs · PRB = 120 packs)</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>• Main เก็บเฉพาะ Cotton + Box · ไม่มีซองเศษ (เศษซองทั้งหมดอยู่ที่ User)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• full_boxes = กล่องครบที่ไม่ได้อยู่ในลัง</t>
+          <t>• full_cottons = ลังใหญ่ครบ (1 cotton = 12 box · OP/EB = 144 packs · PRB = 120 packs)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>• loose_packs = ซองที่ไม่ครบกล่อง</t>
+          <t>• full_boxes = กล่องครบที่ไม่ได้อยู่ในลัง</t>
         </is>
       </c>
     </row>
@@ -666,43 +666,67 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>ห้ามแก้</t>
+          <t>วิธีกรอก Sheet 'User_Stock'</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>• Sheet README นี้</t>
+          <t>• User เก็บได้ทั้ง Cotton/Box/Pack · นับรวมเป็น 'ซอง' ทั้งหมด</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>• Column A-D ใน Main_Stock (sku_id / series / packs_per_box / packs_per_cotton)</t>
+          <t>• ใส่จำนวน 'ซองรวม' ที่ผู้ใช้ถือเหลือในมือ (หลังเติมตู้แล้ว)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>• User Reference ด้านล่าง User_Stock</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>ห้ามแก้</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>คำถาม</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>• Sheet README นี้</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>• Column A-D ใน Main_Stock (sku_id / series / packs_per_box / packs_per_cotton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>• User Reference ด้านล่าง User_Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>คำถาม</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>ถ้าไม่แน่ใจ → ทักเจ้าของระบบ (อย่าเดา) · ตัวเลขผิดยอดสต็อกพังหมดเดือน</t>
         </is>
@@ -719,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -728,10 +752,9 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -744,7 +767,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>กรอกเฉพาะ column สีครีม: full_cottons (ลังใหญ่ครบ) · full_boxes (กล่องครบ) · loose_packs (ซองเหลือ) · unit_cost_per_pack (ราคาใบเสร็จล่าสุด) · note</t>
+          <t>Main เก็บเฉพาะ Cotton + Box · ไม่มีซองเศษ (เศษอยู่ที่ User) · กรอก full_cottons (ลังใหญ่) + full_boxes (กล่อง) + unit_cost_per_pack (ราคาใบเสร็จล่าสุด)</t>
         </is>
       </c>
     </row>
@@ -781,20 +804,15 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>loose_packs</t>
+          <t>total_packs (auto)</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>total_packs (auto)</t>
+          <t>unit_cost_per_pack</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>unit_cost_per_pack</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -823,17 +841,14 @@
       <c r="F4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="8">
-        <f>E4*D4+F4*C4+G4</f>
+      <c r="G4" s="8">
+        <f>E4*D4+F4*C4</f>
         <v/>
       </c>
-      <c r="I4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9" t="inlineStr"/>
+      <c r="H4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -858,17 +873,14 @@
       <c r="F5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8">
-        <f>E5*D5+F5*C5+G5</f>
+      <c r="G5" s="8">
+        <f>E5*D5+F5*C5</f>
         <v/>
       </c>
-      <c r="I5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9" t="inlineStr"/>
+      <c r="H5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -893,17 +905,14 @@
       <c r="F6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
-        <f>E6*D6+F6*C6+G6</f>
+      <c r="G6" s="8">
+        <f>E6*D6+F6*C6</f>
         <v/>
       </c>
-      <c r="I6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9" t="inlineStr"/>
+      <c r="H6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -928,17 +937,14 @@
       <c r="F7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <f>E7*D7+F7*C7+G7</f>
+      <c r="G7" s="8">
+        <f>E7*D7+F7*C7</f>
         <v/>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="9" t="inlineStr"/>
+      <c r="H7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -963,17 +969,14 @@
       <c r="F8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="8">
-        <f>E8*D8+F8*C8+G8</f>
+      <c r="G8" s="8">
+        <f>E8*D8+F8*C8</f>
         <v/>
       </c>
-      <c r="I8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="9" t="inlineStr"/>
+      <c r="H8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -998,17 +1001,14 @@
       <c r="F9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8">
-        <f>E9*D9+F9*C9+G9</f>
+      <c r="G9" s="8">
+        <f>E9*D9+F9*C9</f>
         <v/>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="9" t="inlineStr"/>
+      <c r="H9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1033,17 +1033,14 @@
       <c r="F10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8">
-        <f>E10*D10+F10*C10+G10</f>
+      <c r="G10" s="8">
+        <f>E10*D10+F10*C10</f>
         <v/>
       </c>
-      <c r="I10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="9" t="inlineStr"/>
+      <c r="H10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1068,17 +1065,14 @@
       <c r="F11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8">
-        <f>E11*D11+F11*C11+G11</f>
+      <c r="G11" s="8">
+        <f>E11*D11+F11*C11</f>
         <v/>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="9" t="inlineStr"/>
+      <c r="H11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1103,17 +1097,14 @@
       <c r="F12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="8">
-        <f>E12*D12+F12*C12+G12</f>
+      <c r="G12" s="8">
+        <f>E12*D12+F12*C12</f>
         <v/>
       </c>
-      <c r="I12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9" t="inlineStr"/>
+      <c r="H12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1138,17 +1129,14 @@
       <c r="F13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8">
-        <f>E13*D13+F13*C13+G13</f>
+      <c r="G13" s="8">
+        <f>E13*D13+F13*C13</f>
         <v/>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="9" t="inlineStr"/>
+      <c r="H13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1173,17 +1161,14 @@
       <c r="F14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8">
-        <f>E14*D14+F14*C14+G14</f>
+      <c r="G14" s="8">
+        <f>E14*D14+F14*C14</f>
         <v/>
       </c>
-      <c r="I14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9" t="inlineStr"/>
+      <c r="H14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1208,17 +1193,14 @@
       <c r="F15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8">
-        <f>E15*D15+F15*C15+G15</f>
+      <c r="G15" s="8">
+        <f>E15*D15+F15*C15</f>
         <v/>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="9" t="inlineStr"/>
+      <c r="H15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1243,17 +1225,14 @@
       <c r="F16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8">
-        <f>E16*D16+F16*C16+G16</f>
+      <c r="G16" s="8">
+        <f>E16*D16+F16*C16</f>
         <v/>
       </c>
-      <c r="I16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9" t="inlineStr"/>
+      <c r="H16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1278,17 +1257,14 @@
       <c r="F17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8">
-        <f>E17*D17+F17*C17+G17</f>
+      <c r="G17" s="8">
+        <f>E17*D17+F17*C17</f>
         <v/>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="9" t="inlineStr"/>
+      <c r="H17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1313,17 +1289,14 @@
       <c r="F18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="8">
-        <f>E18*D18+F18*C18+G18</f>
+      <c r="G18" s="8">
+        <f>E18*D18+F18*C18</f>
         <v/>
       </c>
-      <c r="I18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="9" t="inlineStr"/>
+      <c r="H18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1348,17 +1321,14 @@
       <c r="F19" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="8">
-        <f>E19*D19+F19*C19+G19</f>
+      <c r="G19" s="8">
+        <f>E19*D19+F19*C19</f>
         <v/>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="9" t="inlineStr"/>
+      <c r="H19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1383,17 +1353,14 @@
       <c r="F20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="8">
-        <f>E20*D20+F20*C20+G20</f>
+      <c r="G20" s="8">
+        <f>E20*D20+F20*C20</f>
         <v/>
       </c>
-      <c r="I20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="9" t="inlineStr"/>
+      <c r="H20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1418,17 +1385,14 @@
       <c r="F21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8">
-        <f>E21*D21+F21*C21+G21</f>
+      <c r="G21" s="8">
+        <f>E21*D21+F21*C21</f>
         <v/>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="9" t="inlineStr"/>
+      <c r="H21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1453,17 +1417,14 @@
       <c r="F22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="8">
-        <f>E22*D22+F22*C22+G22</f>
+      <c r="G22" s="8">
+        <f>E22*D22+F22*C22</f>
         <v/>
       </c>
-      <c r="I22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="9" t="inlineStr"/>
+      <c r="H22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1488,17 +1449,14 @@
       <c r="F23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="8">
-        <f>E23*D23+F23*C23+G23</f>
+      <c r="G23" s="8">
+        <f>E23*D23+F23*C23</f>
         <v/>
       </c>
-      <c r="I23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="9" t="inlineStr"/>
+      <c r="H23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1523,22 +1481,19 @@
       <c r="F24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8">
-        <f>E24*D24+F24*C24+G24</f>
+      <c r="G24" s="8">
+        <f>E24*D24+F24*C24</f>
         <v/>
       </c>
-      <c r="I24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="9" t="inlineStr"/>
+      <c r="H24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/database/golive_20260501/golive_template.xlsx
+++ b/backend/database/golive_20260501/golive_template.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +49,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002C5282"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -112,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -143,10 +148,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -512,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="115" customWidth="1" min="1" max="1"/>
@@ -635,98 +642,112 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>• username ต้องตรงกับ User Reference ด้านล่างของ sheet</t>
+          <t>• User เก็บได้ทั้ง Cotton/Box/Pack · กรอกแยกหน่วย</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>• 1 row = 1 ผู้ใช้ × 1 SKU (เพิ่ม row ตามต้องการ)</t>
+          <t>• username ต้องตรงกับ User Reference ด้านล่างของ sheet</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>• total_packs = ซองที่ผู้ใช้คนนั้น 'เหลือในมือ' หลังจากเติมตู้แล้ว</t>
+          <t>• 1 row = 1 ผู้ใช้ × 1 SKU (เพิ่ม row ตามต้องการ)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>• full_cottons + full_boxes + loose_packs = ของที่ผู้ใช้คนนั้น 'เหลือในมือ' หลังเติมตู้</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>• total_packs = ระบบคำนวณให้อัตโนมัติ (VLOOKUP packs_per_box จาก SKU Reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>• ถ้าผู้ใช้ไม่มี SKU ใดเลย ข้ามได้</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>วิธีกรอก Sheet 'User_Stock'</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>• User เก็บได้ทั้ง Cotton/Box/Pack · นับรวมเป็น 'ซอง' ทั้งหมด</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>• ใส่จำนวน 'ซองรวม' ที่ผู้ใช้ถือเหลือในมือ (หลังเติมตู้แล้ว)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>ห้ามแก้</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>• Sheet README นี้</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>• Column A-D ใน Main_Stock (sku_id / series / packs_per_box / packs_per_cotton)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>• Sheet README นี้</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>• Column A-D ใน Main_Stock (sku_id / series / packs_per_box / packs_per_cotton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>• User Reference ด้านล่าง User_Stock</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>คำถาม</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>ถ้าไม่แน่ใจ → ทักเจ้าของระบบ (อย่าเดา) · ตัวเลขผิดยอดสต็อกพังหมดเดือน</t>
         </is>
@@ -1505,14 +1526,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1525,7 +1550,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>เพิ่ม 1 row ต่อ (ผู้ใช้, SKU) · username ตรงกับ User Reference ด้านล่าง · total_packs = ซอง (ของที่เหลือในมือ ไม่รวมที่เติมไปในตู้แล้ว)</t>
+          <t>เพิ่ม 1 row ต่อ (ผู้ใช้, SKU) · กรอก full_cottons + full_boxes + loose_packs · ระบบคำนวณ total_packs ให้เอง (ดู SKU Reference ด้านล่างเพื่อเทียบขนาด)</t>
         </is>
       </c>
     </row>
@@ -1537,464 +1562,947 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
+          <t>sku_id</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>full_cottons</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>full_boxes</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>loose_packs</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>total_packs (auto)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>🎴 SKU Reference (อ้างอิง)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="14">
+        <f>IF(B5="","",C5*IFERROR(VLOOKUP(B5,$J$5:$K$25,2,FALSE),0)*12+D5*IFERROR(VLOOKUP(B5,$J$5:$K$25,2,FALSE),0)+E5)</f>
+        <v/>
+      </c>
+      <c r="G5" s="13" t="n"/>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>OP 01</t>
+        </is>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="14">
+        <f>IF(B6="","",C6*IFERROR(VLOOKUP(B6,$J$5:$K$25,2,FALSE),0)*12+D6*IFERROR(VLOOKUP(B6,$J$5:$K$25,2,FALSE),0)+E6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="13" t="n"/>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>OP 02</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="14">
+        <f>IF(B7="","",C7*IFERROR(VLOOKUP(B7,$J$5:$K$25,2,FALSE),0)*12+D7*IFERROR(VLOOKUP(B7,$J$5:$K$25,2,FALSE),0)+E7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="13" t="n"/>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>OP 03</t>
+        </is>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="14">
+        <f>IF(B8="","",C8*IFERROR(VLOOKUP(B8,$J$5:$K$25,2,FALSE),0)*12+D8*IFERROR(VLOOKUP(B8,$J$5:$K$25,2,FALSE),0)+E8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="13" t="n"/>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>OP 04</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="14">
+        <f>IF(B9="","",C9*IFERROR(VLOOKUP(B9,$J$5:$K$25,2,FALSE),0)*12+D9*IFERROR(VLOOKUP(B9,$J$5:$K$25,2,FALSE),0)+E9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="13" t="n"/>
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t>OP 05</t>
+        </is>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="14">
+        <f>IF(B10="","",C10*IFERROR(VLOOKUP(B10,$J$5:$K$25,2,FALSE),0)*12+D10*IFERROR(VLOOKUP(B10,$J$5:$K$25,2,FALSE),0)+E10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="13" t="n"/>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>OP 06</t>
+        </is>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="14">
+        <f>IF(B11="","",C11*IFERROR(VLOOKUP(B11,$J$5:$K$25,2,FALSE),0)*12+D11*IFERROR(VLOOKUP(B11,$J$5:$K$25,2,FALSE),0)+E11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="13" t="n"/>
+      <c r="J11" s="15" t="inlineStr">
+        <is>
+          <t>OP 07</t>
+        </is>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="14">
+        <f>IF(B12="","",C12*IFERROR(VLOOKUP(B12,$J$5:$K$25,2,FALSE),0)*12+D12*IFERROR(VLOOKUP(B12,$J$5:$K$25,2,FALSE),0)+E12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="13" t="n"/>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>OP 08</t>
+        </is>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="14">
+        <f>IF(B13="","",C13*IFERROR(VLOOKUP(B13,$J$5:$K$25,2,FALSE),0)*12+D13*IFERROR(VLOOKUP(B13,$J$5:$K$25,2,FALSE),0)+E13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="13" t="n"/>
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t>OP 09</t>
+        </is>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="14">
+        <f>IF(B14="","",C14*IFERROR(VLOOKUP(B14,$J$5:$K$25,2,FALSE),0)*12+D14*IFERROR(VLOOKUP(B14,$J$5:$K$25,2,FALSE),0)+E14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="13" t="n"/>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>OP 10</t>
+        </is>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="14">
+        <f>IF(B15="","",C15*IFERROR(VLOOKUP(B15,$J$5:$K$25,2,FALSE),0)*12+D15*IFERROR(VLOOKUP(B15,$J$5:$K$25,2,FALSE),0)+E15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="13" t="n"/>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>OP 11</t>
+        </is>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="14">
+        <f>IF(B16="","",C16*IFERROR(VLOOKUP(B16,$J$5:$K$25,2,FALSE),0)*12+D16*IFERROR(VLOOKUP(B16,$J$5:$K$25,2,FALSE),0)+E16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="13" t="n"/>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>OP 12</t>
+        </is>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="14">
+        <f>IF(B17="","",C17*IFERROR(VLOOKUP(B17,$J$5:$K$25,2,FALSE),0)*12+D17*IFERROR(VLOOKUP(B17,$J$5:$K$25,2,FALSE),0)+E17)</f>
+        <v/>
+      </c>
+      <c r="G17" s="13" t="n"/>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>OP 13</t>
+        </is>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="14">
+        <f>IF(B18="","",C18*IFERROR(VLOOKUP(B18,$J$5:$K$25,2,FALSE),0)*12+D18*IFERROR(VLOOKUP(B18,$J$5:$K$25,2,FALSE),0)+E18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="13" t="n"/>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>OP 14</t>
+        </is>
+      </c>
+      <c r="K18" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="14">
+        <f>IF(B19="","",C19*IFERROR(VLOOKUP(B19,$J$5:$K$25,2,FALSE),0)*12+D19*IFERROR(VLOOKUP(B19,$J$5:$K$25,2,FALSE),0)+E19)</f>
+        <v/>
+      </c>
+      <c r="G19" s="13" t="n"/>
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>OP 15</t>
+        </is>
+      </c>
+      <c r="K19" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="14">
+        <f>IF(B20="","",C20*IFERROR(VLOOKUP(B20,$J$5:$K$25,2,FALSE),0)*12+D20*IFERROR(VLOOKUP(B20,$J$5:$K$25,2,FALSE),0)+E20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="13" t="n"/>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>EB 01</t>
+        </is>
+      </c>
+      <c r="K20" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="14">
+        <f>IF(B21="","",C21*IFERROR(VLOOKUP(B21,$J$5:$K$25,2,FALSE),0)*12+D21*IFERROR(VLOOKUP(B21,$J$5:$K$25,2,FALSE),0)+E21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="13" t="n"/>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>EB 02</t>
+        </is>
+      </c>
+      <c r="K21" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="14">
+        <f>IF(B22="","",C22*IFERROR(VLOOKUP(B22,$J$5:$K$25,2,FALSE),0)*12+D22*IFERROR(VLOOKUP(B22,$J$5:$K$25,2,FALSE),0)+E22)</f>
+        <v/>
+      </c>
+      <c r="G22" s="13" t="n"/>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>EB 03</t>
+        </is>
+      </c>
+      <c r="K22" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="14">
+        <f>IF(B23="","",C23*IFERROR(VLOOKUP(B23,$J$5:$K$25,2,FALSE),0)*12+D23*IFERROR(VLOOKUP(B23,$J$5:$K$25,2,FALSE),0)+E23)</f>
+        <v/>
+      </c>
+      <c r="G23" s="13" t="n"/>
+      <c r="J23" s="15" t="inlineStr">
+        <is>
+          <t>EB 04</t>
+        </is>
+      </c>
+      <c r="K23" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="14">
+        <f>IF(B24="","",C24*IFERROR(VLOOKUP(B24,$J$5:$K$25,2,FALSE),0)*12+D24*IFERROR(VLOOKUP(B24,$J$5:$K$25,2,FALSE),0)+E24)</f>
+        <v/>
+      </c>
+      <c r="G24" s="13" t="n"/>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>PRB 01</t>
+        </is>
+      </c>
+      <c r="K24" s="15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="14">
+        <f>IF(B25="","",C25*IFERROR(VLOOKUP(B25,$J$5:$K$25,2,FALSE),0)*12+D25*IFERROR(VLOOKUP(B25,$J$5:$K$25,2,FALSE),0)+E25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="13" t="n"/>
+      <c r="J25" s="15" t="inlineStr">
+        <is>
+          <t>PRB 02</t>
+        </is>
+      </c>
+      <c r="K25" s="15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="14">
+        <f>IF(B26="","",C26*IFERROR(VLOOKUP(B26,$J$5:$K$25,2,FALSE),0)*12+D26*IFERROR(VLOOKUP(B26,$J$5:$K$25,2,FALSE),0)+E26)</f>
+        <v/>
+      </c>
+      <c r="G26" s="13" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="14">
+        <f>IF(B27="","",C27*IFERROR(VLOOKUP(B27,$J$5:$K$25,2,FALSE),0)*12+D27*IFERROR(VLOOKUP(B27,$J$5:$K$25,2,FALSE),0)+E27)</f>
+        <v/>
+      </c>
+      <c r="G27" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="14">
+        <f>IF(B28="","",C28*IFERROR(VLOOKUP(B28,$J$5:$K$25,2,FALSE),0)*12+D28*IFERROR(VLOOKUP(B28,$J$5:$K$25,2,FALSE),0)+E28)</f>
+        <v/>
+      </c>
+      <c r="G28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="14">
+        <f>IF(B29="","",C29*IFERROR(VLOOKUP(B29,$J$5:$K$25,2,FALSE),0)*12+D29*IFERROR(VLOOKUP(B29,$J$5:$K$25,2,FALSE),0)+E29)</f>
+        <v/>
+      </c>
+      <c r="G29" s="13" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="14">
+        <f>IF(B30="","",C30*IFERROR(VLOOKUP(B30,$J$5:$K$25,2,FALSE),0)*12+D30*IFERROR(VLOOKUP(B30,$J$5:$K$25,2,FALSE),0)+E30)</f>
+        <v/>
+      </c>
+      <c r="G30" s="13" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="14">
+        <f>IF(B31="","",C31*IFERROR(VLOOKUP(B31,$J$5:$K$25,2,FALSE),0)*12+D31*IFERROR(VLOOKUP(B31,$J$5:$K$25,2,FALSE),0)+E31)</f>
+        <v/>
+      </c>
+      <c r="G31" s="13" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="14">
+        <f>IF(B32="","",C32*IFERROR(VLOOKUP(B32,$J$5:$K$25,2,FALSE),0)*12+D32*IFERROR(VLOOKUP(B32,$J$5:$K$25,2,FALSE),0)+E32)</f>
+        <v/>
+      </c>
+      <c r="G32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="13" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="14">
+        <f>IF(B33="","",C33*IFERROR(VLOOKUP(B33,$J$5:$K$25,2,FALSE),0)*12+D33*IFERROR(VLOOKUP(B33,$J$5:$K$25,2,FALSE),0)+E33)</f>
+        <v/>
+      </c>
+      <c r="G33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="13" t="n"/>
+      <c r="D34" s="13" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="14">
+        <f>IF(B34="","",C34*IFERROR(VLOOKUP(B34,$J$5:$K$25,2,FALSE),0)*12+D34*IFERROR(VLOOKUP(B34,$J$5:$K$25,2,FALSE),0)+E34)</f>
+        <v/>
+      </c>
+      <c r="G34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n"/>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="13" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="14">
+        <f>IF(B35="","",C35*IFERROR(VLOOKUP(B35,$J$5:$K$25,2,FALSE),0)*12+D35*IFERROR(VLOOKUP(B35,$J$5:$K$25,2,FALSE),0)+E35)</f>
+        <v/>
+      </c>
+      <c r="G35" s="13" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="13" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="14">
+        <f>IF(B36="","",C36*IFERROR(VLOOKUP(B36,$J$5:$K$25,2,FALSE),0)*12+D36*IFERROR(VLOOKUP(B36,$J$5:$K$25,2,FALSE),0)+E36)</f>
+        <v/>
+      </c>
+      <c r="G36" s="13" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="14">
+        <f>IF(B37="","",C37*IFERROR(VLOOKUP(B37,$J$5:$K$25,2,FALSE),0)*12+D37*IFERROR(VLOOKUP(B37,$J$5:$K$25,2,FALSE),0)+E37)</f>
+        <v/>
+      </c>
+      <c r="G37" s="13" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="14">
+        <f>IF(B38="","",C38*IFERROR(VLOOKUP(B38,$J$5:$K$25,2,FALSE),0)*12+D38*IFERROR(VLOOKUP(B38,$J$5:$K$25,2,FALSE),0)+E38)</f>
+        <v/>
+      </c>
+      <c r="G38" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="13" t="n"/>
+      <c r="D39" s="13" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="14">
+        <f>IF(B39="","",C39*IFERROR(VLOOKUP(B39,$J$5:$K$25,2,FALSE),0)*12+D39*IFERROR(VLOOKUP(B39,$J$5:$K$25,2,FALSE),0)+E39)</f>
+        <v/>
+      </c>
+      <c r="G39" s="13" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="13" t="n"/>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="14">
+        <f>IF(B40="","",C40*IFERROR(VLOOKUP(B40,$J$5:$K$25,2,FALSE),0)*12+D40*IFERROR(VLOOKUP(B40,$J$5:$K$25,2,FALSE),0)+E40)</f>
+        <v/>
+      </c>
+      <c r="G40" s="13" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="13" t="n"/>
+      <c r="C41" s="13" t="n"/>
+      <c r="D41" s="13" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="14">
+        <f>IF(B41="","",C41*IFERROR(VLOOKUP(B41,$J$5:$K$25,2,FALSE),0)*12+D41*IFERROR(VLOOKUP(B41,$J$5:$K$25,2,FALSE),0)+E41)</f>
+        <v/>
+      </c>
+      <c r="G41" s="13" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="13" t="n"/>
+      <c r="C42" s="13" t="n"/>
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="14">
+        <f>IF(B42="","",C42*IFERROR(VLOOKUP(B42,$J$5:$K$25,2,FALSE),0)*12+D42*IFERROR(VLOOKUP(B42,$J$5:$K$25,2,FALSE),0)+E42)</f>
+        <v/>
+      </c>
+      <c r="G42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="13" t="n"/>
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="14">
+        <f>IF(B43="","",C43*IFERROR(VLOOKUP(B43,$J$5:$K$25,2,FALSE),0)*12+D43*IFERROR(VLOOKUP(B43,$J$5:$K$25,2,FALSE),0)+E43)</f>
+        <v/>
+      </c>
+      <c r="G43" s="13" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n"/>
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="13" t="n"/>
+      <c r="D44" s="13" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="14">
+        <f>IF(B44="","",C44*IFERROR(VLOOKUP(B44,$J$5:$K$25,2,FALSE),0)*12+D44*IFERROR(VLOOKUP(B44,$J$5:$K$25,2,FALSE),0)+E44)</f>
+        <v/>
+      </c>
+      <c r="G44" s="13" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="n"/>
+      <c r="B45" s="13" t="n"/>
+      <c r="C45" s="13" t="n"/>
+      <c r="D45" s="13" t="n"/>
+      <c r="E45" s="13" t="n"/>
+      <c r="F45" s="14">
+        <f>IF(B45="","",C45*IFERROR(VLOOKUP(B45,$J$5:$K$25,2,FALSE),0)*12+D45*IFERROR(VLOOKUP(B45,$J$5:$K$25,2,FALSE),0)+E45)</f>
+        <v/>
+      </c>
+      <c r="G45" s="13" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="n"/>
+      <c r="B46" s="13" t="n"/>
+      <c r="C46" s="13" t="n"/>
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="14">
+        <f>IF(B46="","",C46*IFERROR(VLOOKUP(B46,$J$5:$K$25,2,FALSE),0)*12+D46*IFERROR(VLOOKUP(B46,$J$5:$K$25,2,FALSE),0)+E46)</f>
+        <v/>
+      </c>
+      <c r="G46" s="13" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="n"/>
+      <c r="B47" s="13" t="n"/>
+      <c r="C47" s="13" t="n"/>
+      <c r="D47" s="13" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="14">
+        <f>IF(B47="","",C47*IFERROR(VLOOKUP(B47,$J$5:$K$25,2,FALSE),0)*12+D47*IFERROR(VLOOKUP(B47,$J$5:$K$25,2,FALSE),0)+E47)</f>
+        <v/>
+      </c>
+      <c r="G47" s="13" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="n"/>
+      <c r="B48" s="13" t="n"/>
+      <c r="C48" s="13" t="n"/>
+      <c r="D48" s="13" t="n"/>
+      <c r="E48" s="13" t="n"/>
+      <c r="F48" s="14">
+        <f>IF(B48="","",C48*IFERROR(VLOOKUP(B48,$J$5:$K$25,2,FALSE),0)*12+D48*IFERROR(VLOOKUP(B48,$J$5:$K$25,2,FALSE),0)+E48)</f>
+        <v/>
+      </c>
+      <c r="G48" s="13" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="n"/>
+      <c r="B49" s="13" t="n"/>
+      <c r="C49" s="13" t="n"/>
+      <c r="D49" s="13" t="n"/>
+      <c r="E49" s="13" t="n"/>
+      <c r="F49" s="14">
+        <f>IF(B49="","",C49*IFERROR(VLOOKUP(B49,$J$5:$K$25,2,FALSE),0)*12+D49*IFERROR(VLOOKUP(B49,$J$5:$K$25,2,FALSE),0)+E49)</f>
+        <v/>
+      </c>
+      <c r="G49" s="13" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="n"/>
+      <c r="B50" s="13" t="n"/>
+      <c r="C50" s="13" t="n"/>
+      <c r="D50" s="13" t="n"/>
+      <c r="E50" s="13" t="n"/>
+      <c r="F50" s="14">
+        <f>IF(B50="","",C50*IFERROR(VLOOKUP(B50,$J$5:$K$25,2,FALSE),0)*12+D50*IFERROR(VLOOKUP(B50,$J$5:$K$25,2,FALSE),0)+E50)</f>
+        <v/>
+      </c>
+      <c r="G50" s="13" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="n"/>
+      <c r="B51" s="13" t="n"/>
+      <c r="C51" s="13" t="n"/>
+      <c r="D51" s="13" t="n"/>
+      <c r="E51" s="13" t="n"/>
+      <c r="F51" s="14">
+        <f>IF(B51="","",C51*IFERROR(VLOOKUP(B51,$J$5:$K$25,2,FALSE),0)*12+D51*IFERROR(VLOOKUP(B51,$J$5:$K$25,2,FALSE),0)+E51)</f>
+        <v/>
+      </c>
+      <c r="G51" s="13" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="n"/>
+      <c r="B52" s="13" t="n"/>
+      <c r="C52" s="13" t="n"/>
+      <c r="D52" s="13" t="n"/>
+      <c r="E52" s="13" t="n"/>
+      <c r="F52" s="14">
+        <f>IF(B52="","",C52*IFERROR(VLOOKUP(B52,$J$5:$K$25,2,FALSE),0)*12+D52*IFERROR(VLOOKUP(B52,$J$5:$K$25,2,FALSE),0)+E52)</f>
+        <v/>
+      </c>
+      <c r="G52" s="13" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="n"/>
+      <c r="B53" s="13" t="n"/>
+      <c r="C53" s="13" t="n"/>
+      <c r="D53" s="13" t="n"/>
+      <c r="E53" s="13" t="n"/>
+      <c r="F53" s="14">
+        <f>IF(B53="","",C53*IFERROR(VLOOKUP(B53,$J$5:$K$25,2,FALSE),0)*12+D53*IFERROR(VLOOKUP(B53,$J$5:$K$25,2,FALSE),0)+E53)</f>
+        <v/>
+      </c>
+      <c r="G53" s="13" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="n"/>
+      <c r="B54" s="13" t="n"/>
+      <c r="C54" s="13" t="n"/>
+      <c r="D54" s="13" t="n"/>
+      <c r="E54" s="13" t="n"/>
+      <c r="F54" s="14">
+        <f>IF(B54="","",C54*IFERROR(VLOOKUP(B54,$J$5:$K$25,2,FALSE),0)*12+D54*IFERROR(VLOOKUP(B54,$J$5:$K$25,2,FALSE),0)+E54)</f>
+        <v/>
+      </c>
+      <c r="G54" s="13" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="n"/>
+      <c r="B55" s="13" t="n"/>
+      <c r="C55" s="13" t="n"/>
+      <c r="D55" s="13" t="n"/>
+      <c r="E55" s="13" t="n"/>
+      <c r="F55" s="14">
+        <f>IF(B55="","",C55*IFERROR(VLOOKUP(B55,$J$5:$K$25,2,FALSE),0)*12+D55*IFERROR(VLOOKUP(B55,$J$5:$K$25,2,FALSE),0)+E55)</f>
+        <v/>
+      </c>
+      <c r="G55" s="13" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="n"/>
+      <c r="B56" s="13" t="n"/>
+      <c r="C56" s="13" t="n"/>
+      <c r="D56" s="13" t="n"/>
+      <c r="E56" s="13" t="n"/>
+      <c r="F56" s="14">
+        <f>IF(B56="","",C56*IFERROR(VLOOKUP(B56,$J$5:$K$25,2,FALSE),0)*12+D56*IFERROR(VLOOKUP(B56,$J$5:$K$25,2,FALSE),0)+E56)</f>
+        <v/>
+      </c>
+      <c r="G56" s="13" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="n"/>
+      <c r="B57" s="13" t="n"/>
+      <c r="C57" s="13" t="n"/>
+      <c r="D57" s="13" t="n"/>
+      <c r="E57" s="13" t="n"/>
+      <c r="F57" s="14">
+        <f>IF(B57="","",C57*IFERROR(VLOOKUP(B57,$J$5:$K$25,2,FALSE),0)*12+D57*IFERROR(VLOOKUP(B57,$J$5:$K$25,2,FALSE),0)+E57)</f>
+        <v/>
+      </c>
+      <c r="G57" s="13" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="n"/>
+      <c r="B58" s="13" t="n"/>
+      <c r="C58" s="13" t="n"/>
+      <c r="D58" s="13" t="n"/>
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="14">
+        <f>IF(B58="","",C58*IFERROR(VLOOKUP(B58,$J$5:$K$25,2,FALSE),0)*12+D58*IFERROR(VLOOKUP(B58,$J$5:$K$25,2,FALSE),0)+E58)</f>
+        <v/>
+      </c>
+      <c r="G58" s="13" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="n"/>
+      <c r="B59" s="13" t="n"/>
+      <c r="C59" s="13" t="n"/>
+      <c r="D59" s="13" t="n"/>
+      <c r="E59" s="13" t="n"/>
+      <c r="F59" s="14">
+        <f>IF(B59="","",C59*IFERROR(VLOOKUP(B59,$J$5:$K$25,2,FALSE),0)*12+D59*IFERROR(VLOOKUP(B59,$J$5:$K$25,2,FALSE),0)+E59)</f>
+        <v/>
+      </c>
+      <c r="G59" s="13" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="n"/>
+      <c r="B60" s="13" t="n"/>
+      <c r="C60" s="13" t="n"/>
+      <c r="D60" s="13" t="n"/>
+      <c r="E60" s="13" t="n"/>
+      <c r="F60" s="14">
+        <f>IF(B60="","",C60*IFERROR(VLOOKUP(B60,$J$5:$K$25,2,FALSE),0)*12+D60*IFERROR(VLOOKUP(B60,$J$5:$K$25,2,FALSE),0)+E60)</f>
+        <v/>
+      </c>
+      <c r="G60" s="13" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="n"/>
+      <c r="B61" s="13" t="n"/>
+      <c r="C61" s="13" t="n"/>
+      <c r="D61" s="13" t="n"/>
+      <c r="E61" s="13" t="n"/>
+      <c r="F61" s="14">
+        <f>IF(B61="","",C61*IFERROR(VLOOKUP(B61,$J$5:$K$25,2,FALSE),0)*12+D61*IFERROR(VLOOKUP(B61,$J$5:$K$25,2,FALSE),0)+E61)</f>
+        <v/>
+      </c>
+      <c r="G61" s="13" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="n"/>
+      <c r="B62" s="13" t="n"/>
+      <c r="C62" s="13" t="n"/>
+      <c r="D62" s="13" t="n"/>
+      <c r="E62" s="13" t="n"/>
+      <c r="F62" s="14">
+        <f>IF(B62="","",C62*IFERROR(VLOOKUP(B62,$J$5:$K$25,2,FALSE),0)*12+D62*IFERROR(VLOOKUP(B62,$J$5:$K$25,2,FALSE),0)+E62)</f>
+        <v/>
+      </c>
+      <c r="G62" s="13" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="n"/>
+      <c r="B63" s="13" t="n"/>
+      <c r="C63" s="13" t="n"/>
+      <c r="D63" s="13" t="n"/>
+      <c r="E63" s="13" t="n"/>
+      <c r="F63" s="14">
+        <f>IF(B63="","",C63*IFERROR(VLOOKUP(B63,$J$5:$K$25,2,FALSE),0)*12+D63*IFERROR(VLOOKUP(B63,$J$5:$K$25,2,FALSE),0)+E63)</f>
+        <v/>
+      </c>
+      <c r="G63" s="13" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="n"/>
+      <c r="B64" s="13" t="n"/>
+      <c r="C64" s="13" t="n"/>
+      <c r="D64" s="13" t="n"/>
+      <c r="E64" s="13" t="n"/>
+      <c r="F64" s="14">
+        <f>IF(B64="","",C64*IFERROR(VLOOKUP(B64,$J$5:$K$25,2,FALSE),0)*12+D64*IFERROR(VLOOKUP(B64,$J$5:$K$25,2,FALSE),0)+E64)</f>
+        <v/>
+      </c>
+      <c r="G64" s="13" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>👥 User Reference (อ้างอิง · อย่าแก้)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>username</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
           <t>display_name</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>sku_id</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>total_packs</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="n"/>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="n"/>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="n"/>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="n"/>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="n"/>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="n"/>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="12" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="n"/>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="12" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="n"/>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="n"/>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="12" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="n"/>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="n"/>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="12" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="n"/>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="12" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="n"/>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="12" t="n"/>
-      <c r="E40" s="12" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="n"/>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="12" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="n"/>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="12" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="n"/>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="n"/>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="n"/>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="12" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="n"/>
-      <c r="B46" s="12" t="n"/>
-      <c r="C46" s="12" t="n"/>
-      <c r="D46" s="12" t="n"/>
-      <c r="E46" s="12" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="12" t="n"/>
-      <c r="B47" s="12" t="n"/>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="12" t="n"/>
-      <c r="E47" s="12" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="n"/>
-      <c r="B48" s="12" t="n"/>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="12" t="n"/>
-      <c r="E48" s="12" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="12" t="n"/>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="12" t="n"/>
-      <c r="E49" s="12" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="n"/>
-      <c r="B50" s="12" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="12" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="12" t="n"/>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="12" t="n"/>
-      <c r="E51" s="12" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="n"/>
-      <c r="B52" s="12" t="n"/>
-      <c r="C52" s="12" t="n"/>
-      <c r="D52" s="12" t="n"/>
-      <c r="E52" s="12" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="12" t="n"/>
-      <c r="B53" s="12" t="n"/>
-      <c r="C53" s="12" t="n"/>
-      <c r="D53" s="12" t="n"/>
-      <c r="E53" s="12" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="n"/>
-      <c r="B54" s="12" t="n"/>
-      <c r="C54" s="12" t="n"/>
-      <c r="D54" s="12" t="n"/>
-      <c r="E54" s="12" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="12" t="n"/>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="12" t="n"/>
-      <c r="E55" s="12" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="n"/>
-      <c r="B56" s="12" t="n"/>
-      <c r="C56" s="12" t="n"/>
-      <c r="D56" s="12" t="n"/>
-      <c r="E56" s="12" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="12" t="n"/>
-      <c r="B57" s="12" t="n"/>
-      <c r="C57" s="12" t="n"/>
-      <c r="D57" s="12" t="n"/>
-      <c r="E57" s="12" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="n"/>
-      <c r="B58" s="12" t="n"/>
-      <c r="C58" s="12" t="n"/>
-      <c r="D58" s="12" t="n"/>
-      <c r="E58" s="12" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="n"/>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="12" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="n"/>
-      <c r="B60" s="12" t="n"/>
-      <c r="C60" s="12" t="n"/>
-      <c r="D60" s="12" t="n"/>
-      <c r="E60" s="12" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="n"/>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="12" t="n"/>
-      <c r="D61" s="12" t="n"/>
-      <c r="E61" s="12" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="n"/>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="12" t="n"/>
-      <c r="D62" s="12" t="n"/>
-      <c r="E62" s="12" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="n"/>
-      <c r="B63" s="12" t="n"/>
-      <c r="C63" s="12" t="n"/>
-      <c r="D63" s="12" t="n"/>
-      <c r="E63" s="12" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="n"/>
-      <c r="B64" s="12" t="n"/>
-      <c r="C64" s="12" t="n"/>
-      <c r="D64" s="12" t="n"/>
-      <c r="E64" s="12" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="13" t="inlineStr">
-        <is>
-          <t>👥 User Reference (อ้างอิง · อย่าแก้)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>username</t>
-        </is>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>display_name</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
+      <c r="C68" s="17" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -2086,9 +2594,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="3">
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
